--- a/inst/extdata/ard-spec/study.xlsx
+++ b/inst/extdata/ard-spec/study.xlsx
@@ -265,7 +265,7 @@
             <name val="Tahoma"/>
           </rPr>
           <t xml:space="preserve">Blank: one cell over cols; each: one cell a column; a key's name: one cell per value of that key (a spanner).
-Example: TR01AG1</t>
+Example: TRTA</t>
         </r>
       </text>
     </comment>
@@ -366,7 +366,7 @@
             <name val="Tahoma"/>
           </rPr>
           <t xml:space="preserve">The key spread across the columns, outermost first, | between them (table_plan(cols = )).
-Example: TRT01A | SEROSTAT</t>
+Example: TRTA | SEX</t>
         </r>
       </text>
     </comment>
@@ -443,8 +443,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">TRUE, FALSE, or the sort keys in order, - in front for descending (plan_sort()); blank: the data's order.
-Example: .overall | group1 | -n | label</t>
+          <t xml:space="preserve">TRUE, FALSE, or the sort keys in order, - in front for descending (plan_sort()): a column, .overall, .depth, a statistic (summed over the columns), stat[col] for one column (-n[Total]), stat@key for a group's own count carried to its rows (-n@group1: SOCs by their own count); blank: the data's order.
+Example: .overall | -n@group1 | group1 | -n | label</t>
         </r>
       </text>
     </comment>
@@ -482,12 +482,194 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Which population {n} in the column header is, for a table split by page (a lab parameter): page (those with that page's data), table (the analysis set), or both as n = page | N = table for {n} and {N}; blank: page (warns when both exist and differ). Both must be in the ARD.
+          <t xml:space="preserve">Which population {n} in the column header is, for a table split by page (a lab parameter): page (those with that page's data), table (the population), or both as n = page | N = table for {n} and {N}; blank: page (warns when both exist and differ). Both must be in the ARD.
 Example: n = page | N = table</t>
         </r>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The heading of a Total column (plan_total()): the ARD's overall rows, its analyses run again without their by (analyses$overall), as one more column; its {n} is the study total. Blank: none.
+Example: Total</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Where the Total column goes among the column key's values: last or first; blank: last.
+Example: first</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The row of a hierarchy's overall counts (a hierarchical analysis with args over_variables = TRUE) and what it prints: normalize_ard(overall = ), written by tfl_normalize_code(). Blank: no such row.
+Example: Subjects with at least one TEAE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">One record's statistics (the same analysis and keys) in named groups (plan_stat_groups()): | between groups, a comma between a group's statistics. The key .stat_group then names them in cols (TRT01A | .stat_group: N in one column, the rate and CI in the next) or in rows (one group under another, in the order said); a cells row's variable may be a group's name, its template one row or several. The ARD stays as it is: no relabelled variable. .variables = RESP limits the groups to those variables, and .others = n puts the other variables' records whole in that group (a subgroup's own n (%) beside its ORR). Blank: none.
+Example: n = N | orr_ci = n, estimate, conf.low, conf.high</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Subgroups as one pair of keys: name = its layers, a comma between them, * crossing variables (AGEGR1 * SEX), | between several keys; or the strata slots (subgroup = group2, group3) (normalize_ard(stack = ), written by tfl_normalize_code()). rows then names subgroup and subgroup_level, whatever group slot each variable came in. Blank: none.
+Example: subgroup = ALL, SEX, AGEGR1, AGEGR1 * SEX</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">What joins a crossed layer's names and levels (AGEGR1 / SEX, 65-80 / F) (normalize_ard(stack_sep = )). Blank: ' / '.
+Example:  x </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE: a crossed layer's outer levels in a key of their own, subgroup_outer, its innermost in subgroup_level, so rows grp = subgroup | outer = subgroup_outer | lvl = subgroup_level with a stub prints the outer level as a heading (normalize_ard(stack_nest = )). Blank: FALSE.
+Example: TRUE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Comparison columns: their names, | between them (plan_compare()). Each reads the ARD's comparison records (a test's p-value, a difference and its CI: the column key with no value) and puts them on the row of their variable; its templates are the cells rows whose variable is the column's name. Blank: none.
+Example: p | diff</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The column that splits the comparisons into columns, one a level (plan_compare(by = )): each active arm against placebo. Blank: one comparison a variable.
+Example: COMPARISON</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Where the comparison columns go: last (blank) or first (plan_compare(position = )).
+Example: first</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Row keys the table also shows as variables, | between them: their own counts (the subgroup variable tabulated by arm) stay in the body, a block of their own beside the subgroup layer of another analysis (table_plan(show_keys = )). Blank: none.
+Example: SEX | AGEGR1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Rows kept by a condition over the record (plan_filter()): one R condition over its statistics and keys, as a cells row's when (p &gt;= 0.05); several joined by &amp;. A SOC stays when one of its PTs does; the overall row always stays. Blank: every row.
+Example: p &gt;= 0.05</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">TRUE / FALSE: the condition in any column (TRUE, blank) or every column (FALSE) (plan_filter(any = )).
+Example: FALSE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">keep (blank): a parent row (a SOC) stays exactly when one of its children does; drop: judged by its own counts (plan_filter(parents = )).
+Example: drop</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -587,6 +769,19 @@
         </r>
       </text>
     </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Its rows under one level of another variable: that variable, a colon, the level as the table shows it (plan_nest()); after that row, one indent deeper, its own heading dropped; blank: its own block.
+Example: RACE: Asian</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -947,12 +1142,25 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
+          <t xml:space="preserve">With pages_page_by (one column): each BY page's name from a template, as group_heading: {value} the page's value, {n} its N as the ARD states it (plan_paginate_rows(heading = )); blank: the value.
+Example: Treatment: {value} (N={n})</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
           <t xml:space="preserve">With group_page = TRUE: the column whose values each start a page (plan_paginate_group(col = )); blank: the outermost row key.
 Example: PARAM</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -965,7 +1173,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -978,7 +1186,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -991,7 +1199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1004,7 +1212,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">With group_page = TRUE: each page's name, the heading rtf_tables(auto_section = TRUE) prints, from a template: {value} the page's value, {n} its N as the ARD states it (the page variable's own tabulation, cards::ard_tabulate(adsl, variables = TRT01A)) (plan_paginate_group(heading = )); blank: the value.
+Example: Treatment: {value} (N={n})</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1017,7 +1238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1030,7 +1251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1043,7 +1264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1056,7 +1277,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1069,7 +1290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1082,7 +1303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="U1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1095,7 +1316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1108,7 +1329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1121,7 +1342,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1134,7 +1355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1147,7 +1368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1160,7 +1381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1173,7 +1394,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AB1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1186,7 +1407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1199,7 +1420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1731,7 +1952,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
   <si>
     <t xml:space="preserve">key</t>
   </si>
@@ -1775,6 +1996,48 @@
     <t xml:space="preserve">header_n</t>
   </si>
   <si>
+    <t xml:space="preserve">total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overall_label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stack_sep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stack_nest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compare_by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compare_position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">show_keys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keep_where</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keep_any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keep_parents</t>
+  </si>
+  <si>
     <t xml:space="preserve">note</t>
   </si>
   <si>
@@ -1793,7 +2056,7 @@
     <t xml:space="preserve">AE</t>
   </si>
   <si>
-    <t xml:space="preserve">TRTA | SEX</t>
+    <t xml:space="preserve">TRT01A | SEX</t>
   </si>
   <si>
     <t xml:space="preserve">group1 = AEBODSYS</t>
@@ -1871,6 +2134,9 @@
     <t xml:space="preserve">empty_levels</t>
   </si>
   <si>
+    <t xml:space="preserve">under</t>
+  </si>
+  <si>
     <t xml:space="preserve">AGE</t>
   </si>
   <si>
@@ -1883,7 +2149,7 @@
     <t xml:space="preserve">Age group, n (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;65 | 65-80 | &gt;80</t>
+    <t xml:space="preserve">&lt;65 | &gt;=65</t>
   </si>
   <si>
     <t xml:space="preserve">SEX</t>
@@ -1901,16 +2167,22 @@
     <t xml:space="preserve">Race, n (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">WEIGHTBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight at baseline (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placebo | Xanomeline Low Dose | Xanomeline High Dose</t>
+    <t xml:space="preserve">ECOGBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline ECOG performance status, n (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 | 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline sum of diameters (mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drug X | Control</t>
   </si>
   <si>
     <t xml:space="preserve">Grade 0 | Grade 1 | Grade 2 | All</t>
@@ -2051,6 +2323,9 @@
     <t xml:space="preserve">pages_page_by</t>
   </si>
   <si>
+    <t xml:space="preserve">pages_heading</t>
+  </si>
+  <si>
     <t xml:space="preserve">group_col</t>
   </si>
   <si>
@@ -2066,6 +2341,9 @@
     <t xml:space="preserve">group_keep</t>
   </si>
   <si>
+    <t xml:space="preserve">group_heading</t>
+  </si>
+  <si>
     <t xml:space="preserve">blank_where</t>
   </si>
   <si>
@@ -2183,28 +2461,22 @@
     <t xml:space="preserve">subgroup</t>
   </si>
   <si>
-    <t xml:space="preserve">Placebo_n</t>
+    <t xml:space="preserve">Control_n</t>
   </si>
   <si>
     <t xml:space="preserve">7</t>
   </si>
   <si>
-    <t xml:space="preserve">Placebo_resp</t>
+    <t xml:space="preserve">Control_resp</t>
   </si>
   <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
-    <t xml:space="preserve">Xanomeline High Dose_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xanomeline High Dose_resp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xanomeline Low Dose_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xanomeline Low Dose_resp</t>
+    <t xml:space="preserve">Drug X_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drug X_resp</t>
   </si>
   <si>
     <t xml:space="preserve">Analyte</t>
@@ -2757,31 +3029,31 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="D1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="E1" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="F1" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="G1" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="H1" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="I1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="J1" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="K1" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -2801,39 +3073,39 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="E1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="F1" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="G1" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="H1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="I1" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -2844,19 +3116,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="F3"/>
       <c r="G3"/>
@@ -2865,17 +3137,17 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
@@ -2884,19 +3156,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="F5"/>
       <c r="G5"/>
@@ -2905,13 +3177,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -2922,40 +3194,40 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="F7"/>
       <c r="G7"/>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D8"/>
       <c r="E8" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="F8"/>
       <c r="G8"/>
@@ -2964,19 +3236,19 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D9" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E9" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="F9"/>
       <c r="G9"/>
@@ -2985,13 +3257,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -3002,19 +3274,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="F11"/>
       <c r="G11"/>
@@ -3023,17 +3295,17 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="D12"/>
       <c r="E12" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="F12"/>
       <c r="G12"/>
@@ -3042,19 +3314,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D13" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E13" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="F13"/>
       <c r="G13"/>
@@ -3063,19 +3335,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="D14" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E14" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="F14"/>
       <c r="G14"/>
@@ -3084,13 +3356,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -3101,17 +3373,17 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D16"/>
       <c r="E16" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="F16"/>
       <c r="G16"/>
@@ -3120,17 +3392,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D17"/>
       <c r="E17" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="F17"/>
       <c r="G17"/>
@@ -3139,19 +3411,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D18" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E18" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="F18"/>
       <c r="G18"/>
@@ -3160,13 +3432,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -3177,13 +3449,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -3194,17 +3466,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D21"/>
       <c r="E21" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="F21"/>
       <c r="G21"/>
@@ -3213,17 +3485,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="D22"/>
       <c r="E22" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F22"/>
       <c r="G22"/>
@@ -3232,17 +3504,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D23"/>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="F23"/>
       <c r="G23"/>
@@ -3251,19 +3523,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D24" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E24" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="F24"/>
       <c r="G24"/>
@@ -3292,10 +3564,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -3346,16 +3618,58 @@
       <c r="L1" t="s">
         <v>14</v>
       </c>
+      <c r="M1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -3365,76 +3679,118 @@
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
-      <c r="L2" t="s">
-        <v>18</v>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E3"/>
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I3"/>
       <c r="J3"/>
       <c r="K3"/>
-      <c r="L3" t="s">
-        <v>24</v>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E4"/>
       <c r="F4"/>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
-      <c r="L4" t="s">
-        <v>31</v>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E5"/>
       <c r="F5"/>
@@ -3443,22 +3799,36 @@
       <c r="I5"/>
       <c r="J5"/>
       <c r="K5"/>
-      <c r="L5" t="s">
-        <v>36</v>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -3469,8 +3839,22 @@
       <c r="I6"/>
       <c r="J6"/>
       <c r="K6"/>
-      <c r="L6" t="s">
-        <v>41</v>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3490,188 +3874,221 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F1" t="s">
-        <v>45</v>
+        <v>59</v>
+      </c>
+      <c r="G1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
+      <c r="G2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F3"/>
+      <c r="G3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F4"/>
+      <c r="G4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5"/>
       <c r="F5"/>
+      <c r="G5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E6"/>
+      <c r="E6" t="s">
+        <v>73</v>
+      </c>
       <c r="F6"/>
+      <c r="G6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7" t="s">
-        <v>59</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7"/>
       <c r="F7"/>
+      <c r="G7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="F8"/>
+      <c r="G8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F9"/>
+      <c r="G9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F10"/>
+      <c r="G10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C11"/>
       <c r="D11"/>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="F11"/>
+      <c r="G11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F12"/>
+      <c r="G12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3690,7 +4107,7 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -3699,7 +4116,7 @@
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3719,25 +4136,25 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="H1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2">
@@ -3747,278 +4164,278 @@
       <c r="D2"/>
       <c r="E2"/>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G3" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="H4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="G5" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="H5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="G9"/>
       <c r="H9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="G10"/>
       <c r="H10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="G11"/>
       <c r="H11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
       <c r="H13" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14"/>
       <c r="H14" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="H16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="H17"/>
     </row>
@@ -4039,13 +4456,13 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4065,96 +4482,102 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C1" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="E1" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="F1" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="G1" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="H1" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="I1" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="J1" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="K1" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="L1" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="M1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="N1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="O1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="P1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="Q1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="R1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="S1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="T1" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="U1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="V1" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="W1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="X1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="Y1" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="Z1" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="AA1" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="AB1" t="s">
-        <v>126</v>
+        <v>143</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -4165,42 +4588,44 @@
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
-      <c r="M2" t="s">
-        <v>129</v>
-      </c>
-      <c r="N2" t="s">
-        <v>130</v>
-      </c>
+      <c r="M2"/>
+      <c r="N2"/>
       <c r="O2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2" t="s">
-        <v>131</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="P2" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2"/>
       <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2" t="s">
-        <v>130</v>
-      </c>
+      <c r="T2" t="s">
+        <v>150</v>
+      </c>
+      <c r="U2"/>
       <c r="V2"/>
-      <c r="W2"/>
+      <c r="W2" t="s">
+        <v>149</v>
+      </c>
       <c r="X2"/>
       <c r="Y2"/>
       <c r="Z2"/>
       <c r="AA2"/>
       <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -4211,69 +4636,71 @@
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
-      <c r="M3" t="s">
-        <v>129</v>
-      </c>
-      <c r="N3" t="s">
-        <v>130</v>
-      </c>
+      <c r="M3"/>
+      <c r="N3"/>
       <c r="O3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="P3" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q3"/>
+        <v>149</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>149</v>
+      </c>
       <c r="R3" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="S3"/>
-      <c r="T3"/>
-      <c r="U3" t="s">
-        <v>130</v>
-      </c>
+      <c r="T3" t="s">
+        <v>150</v>
+      </c>
+      <c r="U3"/>
       <c r="V3"/>
-      <c r="W3"/>
+      <c r="W3" t="s">
+        <v>149</v>
+      </c>
       <c r="X3"/>
       <c r="Y3"/>
       <c r="Z3"/>
       <c r="AA3"/>
       <c r="AB3"/>
+      <c r="AC3"/>
+      <c r="AD3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4"/>
-      <c r="I4" t="s">
+      <c r="I4"/>
+      <c r="J4" t="s">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
-        <v>135</v>
-      </c>
-      <c r="K4"/>
+      <c r="K4" t="s">
+        <v>154</v>
+      </c>
       <c r="L4"/>
-      <c r="M4" t="s">
-        <v>129</v>
-      </c>
-      <c r="N4" t="s">
-        <v>130</v>
-      </c>
+      <c r="M4"/>
+      <c r="N4"/>
       <c r="O4" t="s">
-        <v>130</v>
-      </c>
-      <c r="P4"/>
-      <c r="Q4"/>
+        <v>148</v>
+      </c>
+      <c r="P4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>149</v>
+      </c>
       <c r="R4"/>
       <c r="S4"/>
       <c r="T4"/>
@@ -4285,10 +4712,12 @@
       <c r="Z4"/>
       <c r="AA4"/>
       <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B5"/>
       <c r="C5"/>
@@ -4299,26 +4728,26 @@
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5"/>
-      <c r="K5" t="s">
-        <v>130</v>
-      </c>
+      <c r="K5"/>
       <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5"/>
-      <c r="N5" t="s">
-        <v>130</v>
-      </c>
-      <c r="O5" t="s">
-        <v>130</v>
-      </c>
-      <c r="P5"/>
-      <c r="Q5"/>
-      <c r="R5" t="s">
-        <v>131</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="M5" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>149</v>
+      </c>
+      <c r="R5"/>
       <c r="S5"/>
-      <c r="T5"/>
+      <c r="T5" t="s">
+        <v>150</v>
+      </c>
       <c r="U5"/>
       <c r="V5"/>
       <c r="W5"/>
@@ -4327,13 +4756,15 @@
       <c r="Z5"/>
       <c r="AA5"/>
       <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -4342,37 +4773,39 @@
       <c r="G6"/>
       <c r="H6"/>
       <c r="I6"/>
-      <c r="J6" t="s">
-        <v>130</v>
-      </c>
-      <c r="K6"/>
+      <c r="J6"/>
+      <c r="K6" t="s">
+        <v>149</v>
+      </c>
       <c r="L6"/>
-      <c r="M6" t="s">
-        <v>129</v>
-      </c>
-      <c r="N6" t="s">
-        <v>130</v>
-      </c>
+      <c r="M6"/>
+      <c r="N6"/>
       <c r="O6" t="s">
-        <v>130</v>
-      </c>
-      <c r="P6"/>
-      <c r="Q6"/>
+        <v>148</v>
+      </c>
+      <c r="P6" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>149</v>
+      </c>
       <c r="R6"/>
       <c r="S6"/>
       <c r="T6"/>
       <c r="U6"/>
-      <c r="V6" t="s">
-        <v>137</v>
-      </c>
+      <c r="V6"/>
       <c r="W6"/>
       <c r="X6" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="Y6"/>
-      <c r="Z6"/>
+      <c r="Z6" t="s">
+        <v>154</v>
+      </c>
       <c r="AA6"/>
       <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4391,30 +4824,30 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="C1" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="D1" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="E1" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="F1" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -4422,13 +4855,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -4436,13 +4869,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -4450,13 +4883,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -4464,45 +4897,45 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E6"/>
       <c r="F6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7" t="s">
         <v>149</v>
-      </c>
-      <c r="C7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D7" t="s">
-        <v>130</v>
       </c>
       <c r="E7"/>
       <c r="F7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -4510,13 +4943,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -4524,13 +4957,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -4538,13 +4971,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -4552,13 +4985,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -4566,13 +4999,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -4580,79 +5013,51 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="C14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14"/>
+        <v>112</v>
+      </c>
+      <c r="D14" t="s">
+        <v>149</v>
+      </c>
       <c r="E14"/>
       <c r="F14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15"/>
+        <v>108</v>
+      </c>
+      <c r="D15" t="s">
+        <v>149</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>130</v>
-      </c>
-      <c r="E16"/>
+        <v>108</v>
+      </c>
+      <c r="D16"/>
+      <c r="E16" t="s">
+        <v>149</v>
+      </c>
       <c r="F16"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" t="s">
-        <v>130</v>
-      </c>
-      <c r="E17"/>
-      <c r="F17"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18"/>
-      <c r="E18" t="s">
-        <v>130</v>
-      </c>
-      <c r="F18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4671,106 +5076,106 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C1" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="E1" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="F1" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="G1" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="H1" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="I1" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J1" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="K1" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="L1" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="M1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="N1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="O1" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="P1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="Q1" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="R1" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="S1" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="T1" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="U1" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="V1" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="W1" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="X1" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="Y1" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="Z1" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="AA1" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="AB1" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="AC1" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="AD1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="AE1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="AF1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -4804,15 +5209,15 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="F3"/>
       <c r="G3"/>
@@ -4844,11 +5249,11 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B4"/>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -4882,11 +5287,11 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B5"/>
       <c r="C5" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
